--- a/Project_01 - Automation_Exercise/Automatic Exercise QA Project.xlsx
+++ b/Project_01 - Automation_Exercise/Automatic Exercise QA Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Clarence\OneDrive\Desktop\Automation Exercise QA Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4831D2-3253-4538-8790-E5295DD1F690}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4D711C-90E7-484B-8A4E-8FD09C089BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{630BC110-9717-401F-A122-0D6508C22400}"/>
   </bookViews>
@@ -17,10 +17,10 @@
     <sheet name="Sign-Up" sheetId="2" r:id="rId2"/>
     <sheet name="Sign-In" sheetId="4" r:id="rId3"/>
     <sheet name="Shopping Cart" sheetId="5" r:id="rId4"/>
-    <sheet name="Product Search &amp; Category Manag" sheetId="6" r:id="rId5"/>
+    <sheet name="PS &amp; CM" sheetId="6" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Product Search &amp; Category Manag'!$A$1:$G$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'PS &amp; CM'!$A$1:$G$37</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Shopping Cart'!$A$1:$G$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Sign-In'!$A$1:$G$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Test Scenarios'!$A$1:$D$17</definedName>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="168">
   <si>
     <t>Project Name</t>
   </si>
@@ -1431,6 +1431,9 @@
   </si>
   <si>
     <t>Products are filtered by brand and the system shows all items relevant to the selection.</t>
+  </si>
+  <si>
+    <t>Sign-in</t>
   </si>
 </sst>
 </file>
@@ -1610,17 +1613,32 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1630,21 +1648,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2044,7 +2047,7 @@
       <c r="A8" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -2058,7 +2061,7 @@
       <c r="A9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
@@ -2070,7 +2073,7 @@
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="13"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
@@ -2082,7 +2085,7 @@
       <c r="A11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
@@ -2094,8 +2097,8 @@
       <c r="A12" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>12</v>
+      <c r="B12" s="15" t="s">
+        <v>167</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>13</v>
@@ -2108,7 +2111,7 @@
       <c r="A13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="13"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
@@ -2134,7 +2137,7 @@
       <c r="A15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="15" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -2148,7 +2151,7 @@
       <c r="A16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="13"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="1" t="s">
         <v>19</v>
       </c>
@@ -2207,37 +2210,37 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>20</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>38</v>
@@ -2245,23 +2248,23 @@
       <c r="D4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="1"/>
       <c r="C6" s="3" t="s">
         <v>40</v>
@@ -2269,47 +2272,47 @@
       <c r="D6" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="1"/>
       <c r="C7" s="3" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="1"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="1"/>
       <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D8" s="1"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
         <v>38</v>
@@ -2317,11 +2320,11 @@
       <c r="D10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
         <v>44</v>
@@ -2329,73 +2332,73 @@
       <c r="D11" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D14" s="1"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="14" t="s">
+      <c r="D16" s="17"/>
+      <c r="E16" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3" t="s">
         <v>48</v>
@@ -2403,23 +2406,23 @@
       <c r="D17" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3" t="s">
         <v>40</v>
@@ -2427,49 +2430,49 @@
       <c r="D19" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D21" s="1"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="14" t="s">
+      <c r="D22" s="17"/>
+      <c r="E22" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3" t="s">
         <v>48</v>
@@ -2477,23 +2480,23 @@
       <c r="D23" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3" t="s">
         <v>40</v>
@@ -2501,49 +2504,49 @@
       <c r="D25" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="14"/>
+      <c r="A26" s="16"/>
       <c r="B26" s="1"/>
       <c r="C26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="14"/>
+      <c r="A27" s="16"/>
       <c r="B27" s="1"/>
       <c r="C27" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D27" s="1"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="14"/>
+      <c r="A28" s="16"/>
       <c r="B28" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="16"/>
-      <c r="E28" s="14" t="s">
+      <c r="D28" s="17"/>
+      <c r="E28" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="14"/>
+      <c r="A29" s="16"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
         <v>48</v>
@@ -2551,11 +2554,11 @@
       <c r="D29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="14"/>
+      <c r="A30" s="16"/>
       <c r="B30" s="1"/>
       <c r="C30" s="3" t="s">
         <v>54</v>
@@ -2563,59 +2566,59 @@
       <c r="D30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="14"/>
+      <c r="A31" s="16"/>
       <c r="B31" s="1"/>
       <c r="C31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
+      <c r="E31" s="16"/>
+      <c r="F31" s="16"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="14"/>
+      <c r="A32" s="16"/>
       <c r="B32" s="1"/>
       <c r="C32" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D32" s="1"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="14"/>
+      <c r="A33" s="16"/>
       <c r="B33" s="1"/>
       <c r="C33" s="3" t="s">
         <v>56</v>
       </c>
       <c r="D33" s="1"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="14"/>
+      <c r="A34" s="16"/>
       <c r="B34" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="D34" s="16"/>
-      <c r="E34" s="14" t="s">
+      <c r="D34" s="17"/>
+      <c r="E34" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="14"/>
+      <c r="A35" s="16"/>
       <c r="B35" s="1"/>
       <c r="C35" s="3" t="s">
         <v>48</v>
@@ -2623,11 +2626,11 @@
       <c r="D35" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="14"/>
+      <c r="A36" s="16"/>
       <c r="B36" s="1"/>
       <c r="C36" s="3" t="s">
         <v>58</v>
@@ -2635,73 +2638,73 @@
       <c r="D36" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
     </row>
     <row r="37" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="14"/>
+      <c r="A37" s="16"/>
       <c r="B37" s="1"/>
       <c r="C37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
+      <c r="A38" s="16"/>
       <c r="B38" s="1"/>
       <c r="C38" s="3" t="s">
         <v>55</v>
       </c>
       <c r="D38" s="1"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="14"/>
+      <c r="A39" s="16"/>
       <c r="B39" s="1"/>
       <c r="C39" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D39" s="1"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="16" t="s">
         <v>22</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="14"/>
+      <c r="A41" s="16"/>
       <c r="B41" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="D41" s="16"/>
-      <c r="E41" s="14" t="s">
+      <c r="D41" s="17"/>
+      <c r="E41" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
+      <c r="A42" s="16"/>
       <c r="B42" s="1"/>
       <c r="C42" s="3" t="s">
         <v>61</v>
@@ -2709,23 +2712,23 @@
       <c r="D42" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="14"/>
+      <c r="A43" s="16"/>
       <c r="B43" s="1"/>
       <c r="C43" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D43" s="20" t="s">
+      <c r="D43" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
+      <c r="A44" s="16"/>
       <c r="B44" s="1"/>
       <c r="C44" s="3" t="s">
         <v>40</v>
@@ -2733,49 +2736,49 @@
       <c r="D44" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="16"/>
     </row>
     <row r="45" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="14"/>
+      <c r="A45" s="16"/>
       <c r="B45" s="1"/>
       <c r="C45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
+      <c r="E45" s="16"/>
+      <c r="F45" s="16"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="14"/>
+      <c r="A46" s="16"/>
       <c r="B46" s="1"/>
       <c r="C46" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D46" s="1"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="14"/>
+      <c r="A47" s="16"/>
       <c r="B47" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="16"/>
-      <c r="E47" s="14" t="s">
+      <c r="D47" s="17"/>
+      <c r="E47" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="14"/>
+      <c r="A48" s="16"/>
       <c r="B48" s="1"/>
       <c r="C48" s="3" t="s">
         <v>61</v>
@@ -2783,11 +2786,11 @@
       <c r="D48" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="14"/>
+      <c r="A49" s="16"/>
       <c r="B49" s="1"/>
       <c r="C49" s="3" t="s">
         <v>64</v>
@@ -2795,73 +2798,73 @@
       <c r="D49" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
+      <c r="E49" s="16"/>
+      <c r="F49" s="16"/>
     </row>
     <row r="50" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="14"/>
+      <c r="A50" s="16"/>
       <c r="B50" s="1"/>
       <c r="C50" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
+      <c r="E50" s="16"/>
+      <c r="F50" s="16"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="14"/>
+      <c r="A51" s="16"/>
       <c r="B51" s="1"/>
       <c r="C51" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D51" s="1"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="16"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="14"/>
+      <c r="A52" s="16"/>
       <c r="B52" s="1"/>
       <c r="C52" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D52" s="1"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="A53" s="16" t="s">
         <v>23</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="15" t="s">
+      <c r="C53" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
+      <c r="D53" s="18"/>
+      <c r="E53" s="18"/>
+      <c r="F53" s="18"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="14"/>
+      <c r="A54" s="16"/>
       <c r="B54" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C54" s="16" t="s">
+      <c r="C54" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D54" s="16"/>
-      <c r="E54" s="14" t="s">
+      <c r="D54" s="17"/>
+      <c r="E54" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="14"/>
+      <c r="A55" s="16"/>
       <c r="B55" s="1"/>
       <c r="C55" s="3" t="s">
         <v>48</v>
@@ -2869,23 +2872,23 @@
       <c r="D55" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="14"/>
+      <c r="A56" s="16"/>
       <c r="B56" s="1"/>
       <c r="C56" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D56" s="20" t="s">
+      <c r="D56" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="14"/>
+      <c r="A57" s="16"/>
       <c r="B57" s="1"/>
       <c r="C57" s="3" t="s">
         <v>40</v>
@@ -2893,49 +2896,49 @@
       <c r="D57" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
     </row>
     <row r="58" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="14"/>
+      <c r="A58" s="16"/>
       <c r="B58" s="1"/>
       <c r="C58" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D58" s="20" t="s">
+      <c r="D58" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="16"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="14"/>
+      <c r="A59" s="16"/>
       <c r="B59" s="1"/>
       <c r="C59" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D59" s="1"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="14"/>
+      <c r="A60" s="16"/>
       <c r="B60" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C60" s="16" t="s">
+      <c r="C60" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D60" s="16"/>
-      <c r="E60" s="14" t="s">
+      <c r="D60" s="17"/>
+      <c r="E60" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F60" s="14" t="s">
+      <c r="F60" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="14"/>
+      <c r="A61" s="16"/>
       <c r="B61" s="1"/>
       <c r="C61" s="3" t="s">
         <v>48</v>
@@ -2943,23 +2946,23 @@
       <c r="D61" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="14"/>
+      <c r="A62" s="16"/>
       <c r="B62" s="1"/>
       <c r="C62" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D62" s="20" t="s">
+      <c r="D62" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="E62" s="16"/>
+      <c r="F62" s="16"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="14"/>
+      <c r="A63" s="16"/>
       <c r="B63" s="1"/>
       <c r="C63" s="3" t="s">
         <v>40</v>
@@ -2967,49 +2970,49 @@
       <c r="D63" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
+      <c r="E63" s="16"/>
+      <c r="F63" s="16"/>
     </row>
     <row r="64" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="14"/>
+      <c r="A64" s="16"/>
       <c r="B64" s="1"/>
       <c r="C64" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D64" s="20" t="s">
+      <c r="D64" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="14"/>
+      <c r="A65" s="16"/>
       <c r="B65" s="1"/>
       <c r="C65" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D65" s="1"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="14"/>
+      <c r="A66" s="16"/>
       <c r="B66" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C66" s="16" t="s">
+      <c r="C66" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D66" s="16"/>
-      <c r="E66" s="14" t="s">
+      <c r="D66" s="17"/>
+      <c r="E66" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="14"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="1"/>
       <c r="C67" s="3" t="s">
         <v>48</v>
@@ -3017,23 +3020,23 @@
       <c r="D67" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="14"/>
+      <c r="A68" s="16"/>
       <c r="B68" s="1"/>
       <c r="C68" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D68" s="20" t="s">
+      <c r="D68" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="14"/>
+      <c r="A69" s="16"/>
       <c r="B69" s="1"/>
       <c r="C69" s="3" t="s">
         <v>40</v>
@@ -3041,49 +3044,49 @@
       <c r="D69" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E69" s="14"/>
-      <c r="F69" s="14"/>
+      <c r="E69" s="16"/>
+      <c r="F69" s="16"/>
     </row>
     <row r="70" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="14"/>
+      <c r="A70" s="16"/>
       <c r="B70" s="1"/>
       <c r="C70" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D70" s="20" t="s">
+      <c r="D70" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="E70" s="14"/>
-      <c r="F70" s="14"/>
+      <c r="E70" s="16"/>
+      <c r="F70" s="16"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="14"/>
+      <c r="A71" s="16"/>
       <c r="B71" s="1"/>
       <c r="C71" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D71" s="1"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="14"/>
+      <c r="E71" s="16"/>
+      <c r="F71" s="16"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
+      <c r="A72" s="16"/>
       <c r="B72" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C72" s="16" t="s">
+      <c r="C72" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D72" s="16"/>
-      <c r="E72" s="14" t="s">
+      <c r="D72" s="17"/>
+      <c r="E72" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="14"/>
+      <c r="A73" s="16"/>
       <c r="B73" s="1"/>
       <c r="C73" s="3" t="s">
         <v>48</v>
@@ -3091,23 +3094,23 @@
       <c r="D73" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E73" s="14"/>
-      <c r="F73" s="14"/>
+      <c r="E73" s="16"/>
+      <c r="F73" s="16"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="14"/>
+      <c r="A74" s="16"/>
       <c r="B74" s="1"/>
       <c r="C74" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D74" s="20" t="s">
+      <c r="D74" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E74" s="14"/>
-      <c r="F74" s="14"/>
+      <c r="E74" s="16"/>
+      <c r="F74" s="16"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A75" s="14"/>
+      <c r="A75" s="16"/>
       <c r="B75" s="1"/>
       <c r="C75" s="3" t="s">
         <v>40</v>
@@ -3115,11 +3118,11 @@
       <c r="D75" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E75" s="14"/>
-      <c r="F75" s="14"/>
+      <c r="E75" s="16"/>
+      <c r="F75" s="16"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="14"/>
+      <c r="A76" s="16"/>
       <c r="B76" s="1"/>
       <c r="C76" s="3" t="s">
         <v>41</v>
@@ -3127,37 +3130,37 @@
       <c r="D76" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E76" s="14"/>
-      <c r="F76" s="14"/>
+      <c r="E76" s="16"/>
+      <c r="F76" s="16"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="14"/>
+      <c r="A77" s="16"/>
       <c r="B77" s="1"/>
       <c r="C77" s="3" t="s">
         <v>42</v>
       </c>
       <c r="D77" s="1"/>
-      <c r="E77" s="14"/>
-      <c r="F77" s="14"/>
+      <c r="E77" s="16"/>
+      <c r="F77" s="16"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" s="14"/>
+      <c r="A78" s="16"/>
       <c r="B78" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C78" s="16" t="s">
+      <c r="C78" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="D78" s="16"/>
-      <c r="E78" s="14" t="s">
+      <c r="D78" s="17"/>
+      <c r="E78" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A79" s="14"/>
+      <c r="A79" s="16"/>
       <c r="B79" s="1"/>
       <c r="C79" s="3" t="s">
         <v>48</v>
@@ -3165,23 +3168,23 @@
       <c r="D79" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="E79" s="14"/>
-      <c r="F79" s="14"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A80" s="14"/>
+      <c r="A80" s="16"/>
       <c r="B80" s="1"/>
       <c r="C80" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D80" s="20" t="s">
+      <c r="D80" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
+      <c r="E80" s="16"/>
+      <c r="F80" s="16"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A81" s="14"/>
+      <c r="A81" s="16"/>
       <c r="B81" s="1"/>
       <c r="C81" s="3" t="s">
         <v>40</v>
@@ -3189,11 +3192,11 @@
       <c r="D81" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
+      <c r="E81" s="16"/>
+      <c r="F81" s="16"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="14"/>
+      <c r="A82" s="16"/>
       <c r="B82" s="1"/>
       <c r="C82" s="3" t="s">
         <v>41</v>
@@ -3201,36 +3204,36 @@
       <c r="D82" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
+      <c r="E82" s="16"/>
+      <c r="F82" s="16"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A83" s="14"/>
+      <c r="A83" s="16"/>
       <c r="B83" s="1"/>
       <c r="C83" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="14"/>
-      <c r="F83" s="14"/>
+      <c r="E83" s="16"/>
+      <c r="F83" s="16"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A84" s="14"/>
+      <c r="A84" s="16"/>
       <c r="B84" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C84" s="16" t="s">
+      <c r="C84" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="D84" s="16"/>
-      <c r="E84" s="14" t="s">
+      <c r="D84" s="17"/>
+      <c r="E84" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F84" s="14" t="s">
+      <c r="F84" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A85" s="14"/>
+      <c r="A85" s="16"/>
       <c r="B85" s="1"/>
       <c r="C85" s="3" t="s">
         <v>48</v>
@@ -3238,11 +3241,11 @@
       <c r="D85" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14"/>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A86" s="14"/>
+      <c r="A86" s="16"/>
       <c r="B86" s="1"/>
       <c r="C86" s="3" t="s">
         <v>78</v>
@@ -3250,59 +3253,59 @@
       <c r="D86" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14"/>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16"/>
     </row>
     <row r="87" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A87" s="14"/>
+      <c r="A87" s="16"/>
       <c r="B87" s="1"/>
       <c r="C87" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="20" t="s">
+      <c r="D87" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
+      <c r="E87" s="16"/>
+      <c r="F87" s="16"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="14"/>
+      <c r="A88" s="16"/>
       <c r="B88" s="1"/>
       <c r="C88" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D88" s="1"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
+      <c r="E88" s="16"/>
+      <c r="F88" s="16"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="14"/>
+      <c r="A89" s="16"/>
       <c r="B89" s="1"/>
       <c r="C89" s="3" t="s">
         <v>150</v>
       </c>
       <c r="D89" s="1"/>
-      <c r="E89" s="14"/>
-      <c r="F89" s="14"/>
+      <c r="E89" s="16"/>
+      <c r="F89" s="16"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="14"/>
+      <c r="A90" s="16"/>
       <c r="B90" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C90" s="16" t="s">
+      <c r="C90" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D90" s="16"/>
-      <c r="E90" s="14" t="s">
+      <c r="D90" s="17"/>
+      <c r="E90" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F90" s="14" t="s">
+      <c r="F90" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A91" s="14"/>
+      <c r="A91" s="16"/>
       <c r="B91" s="1"/>
       <c r="C91" s="3" t="s">
         <v>48</v>
@@ -3310,11 +3313,11 @@
       <c r="D91" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E91" s="14"/>
-      <c r="F91" s="14"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A92" s="14"/>
+      <c r="A92" s="16"/>
       <c r="B92" s="1"/>
       <c r="C92" s="3" t="s">
         <v>80</v>
@@ -3322,59 +3325,59 @@
       <c r="D92" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
+      <c r="E92" s="16"/>
+      <c r="F92" s="16"/>
     </row>
     <row r="93" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A93" s="14"/>
+      <c r="A93" s="16"/>
       <c r="B93" s="1"/>
       <c r="C93" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="20" t="s">
+      <c r="D93" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="E93" s="14"/>
-      <c r="F93" s="14"/>
+      <c r="E93" s="16"/>
+      <c r="F93" s="16"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A94" s="14"/>
+      <c r="A94" s="16"/>
       <c r="B94" s="1"/>
       <c r="C94" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D94" s="1"/>
-      <c r="E94" s="14"/>
-      <c r="F94" s="14"/>
+      <c r="E94" s="16"/>
+      <c r="F94" s="16"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A95" s="14"/>
+      <c r="A95" s="16"/>
       <c r="B95" s="1"/>
       <c r="C95" s="3" t="s">
         <v>81</v>
       </c>
       <c r="D95" s="1"/>
-      <c r="E95" s="14"/>
-      <c r="F95" s="14"/>
+      <c r="E95" s="16"/>
+      <c r="F95" s="16"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A96" s="14"/>
+      <c r="A96" s="16"/>
       <c r="B96" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C96" s="16" t="s">
+      <c r="C96" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="D96" s="16"/>
-      <c r="E96" s="14" t="s">
+      <c r="D96" s="17"/>
+      <c r="E96" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F96" s="14" t="s">
+      <c r="F96" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="14"/>
+      <c r="A97" s="16"/>
       <c r="B97" s="1"/>
       <c r="C97" s="3" t="s">
         <v>48</v>
@@ -3382,11 +3385,11 @@
       <c r="D97" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E97" s="14"/>
-      <c r="F97" s="14"/>
+      <c r="E97" s="16"/>
+      <c r="F97" s="16"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="14"/>
+      <c r="A98" s="16"/>
       <c r="B98" s="1"/>
       <c r="C98" s="3" t="s">
         <v>83</v>
@@ -3394,59 +3397,59 @@
       <c r="D98" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
+      <c r="E98" s="16"/>
+      <c r="F98" s="16"/>
     </row>
     <row r="99" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A99" s="14"/>
+      <c r="A99" s="16"/>
       <c r="B99" s="1"/>
       <c r="C99" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D99" s="20" t="s">
+      <c r="D99" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="E99" s="14"/>
-      <c r="F99" s="14"/>
+      <c r="E99" s="16"/>
+      <c r="F99" s="16"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A100" s="14"/>
+      <c r="A100" s="16"/>
       <c r="B100" s="1"/>
       <c r="C100" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D100" s="1"/>
-      <c r="E100" s="14"/>
-      <c r="F100" s="14"/>
+      <c r="E100" s="16"/>
+      <c r="F100" s="16"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A101" s="14"/>
+      <c r="A101" s="16"/>
       <c r="B101" s="1"/>
       <c r="C101" s="3" t="s">
         <v>153</v>
       </c>
       <c r="D101" s="1"/>
-      <c r="E101" s="14"/>
-      <c r="F101" s="14"/>
+      <c r="E101" s="16"/>
+      <c r="F101" s="16"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A102" s="14"/>
+      <c r="A102" s="16"/>
       <c r="B102" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C102" s="16" t="s">
+      <c r="C102" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="D102" s="16"/>
-      <c r="E102" s="14" t="s">
+      <c r="D102" s="17"/>
+      <c r="E102" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F102" s="14" t="s">
+      <c r="F102" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A103" s="14"/>
+      <c r="A103" s="16"/>
       <c r="B103" s="1"/>
       <c r="C103" s="3" t="s">
         <v>48</v>
@@ -3454,11 +3457,11 @@
       <c r="D103" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="E103" s="14"/>
-      <c r="F103" s="14"/>
+      <c r="E103" s="16"/>
+      <c r="F103" s="16"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A104" s="14"/>
+      <c r="A104" s="16"/>
       <c r="B104" s="1"/>
       <c r="C104" s="3" t="s">
         <v>85</v>
@@ -3466,40 +3469,40 @@
       <c r="D104" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E104" s="14"/>
-      <c r="F104" s="14"/>
+      <c r="E104" s="16"/>
+      <c r="F104" s="16"/>
     </row>
     <row r="105" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A105" s="14"/>
+      <c r="A105" s="16"/>
       <c r="B105" s="1"/>
       <c r="C105" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D105" s="20" t="s">
+      <c r="D105" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="E105" s="14"/>
-      <c r="F105" s="14"/>
+      <c r="E105" s="16"/>
+      <c r="F105" s="16"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A106" s="14"/>
+      <c r="A106" s="16"/>
       <c r="B106" s="1"/>
       <c r="C106" s="3" t="s">
         <v>45</v>
       </c>
       <c r="D106" s="1"/>
-      <c r="E106" s="14"/>
-      <c r="F106" s="14"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A107" s="14"/>
+      <c r="A107" s="16"/>
       <c r="B107" s="1"/>
       <c r="C107" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D107" s="1"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="14"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="59">
@@ -3508,6 +3511,7 @@
     <mergeCell ref="E90:E95"/>
     <mergeCell ref="E96:E101"/>
     <mergeCell ref="E102:E107"/>
+    <mergeCell ref="F90:F95"/>
     <mergeCell ref="C96:D96"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="A53:A107"/>
@@ -3524,27 +3528,28 @@
     <mergeCell ref="C84:D84"/>
     <mergeCell ref="C90:D90"/>
     <mergeCell ref="C54:D54"/>
-    <mergeCell ref="A40:A52"/>
-    <mergeCell ref="E41:E46"/>
-    <mergeCell ref="E47:E52"/>
-    <mergeCell ref="C53:F53"/>
     <mergeCell ref="F84:F89"/>
-    <mergeCell ref="F90:F95"/>
     <mergeCell ref="F54:F59"/>
     <mergeCell ref="F60:F65"/>
     <mergeCell ref="F66:F71"/>
     <mergeCell ref="F72:F77"/>
     <mergeCell ref="F78:F83"/>
+    <mergeCell ref="F34:F39"/>
+    <mergeCell ref="A40:A52"/>
+    <mergeCell ref="E41:E46"/>
+    <mergeCell ref="E47:E52"/>
+    <mergeCell ref="C53:F53"/>
     <mergeCell ref="F41:F46"/>
     <mergeCell ref="F47:F52"/>
     <mergeCell ref="C40:F40"/>
     <mergeCell ref="C41:D41"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="F9:F14"/>
     <mergeCell ref="F16:F21"/>
     <mergeCell ref="F22:F27"/>
     <mergeCell ref="F28:F33"/>
-    <mergeCell ref="F34:F39"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="F3:F8"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A15:A39"/>
     <mergeCell ref="E3:E8"/>
@@ -3560,8 +3565,6 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F3:F8"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="2">
@@ -3617,300 +3620,296 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="22" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
+      <c r="A3" s="23"/>
       <c r="B3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
+      <c r="A5" s="23"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
+      <c r="A6" s="23"/>
       <c r="B6" s="1"/>
       <c r="C6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18"/>
+      <c r="A7" s="23"/>
       <c r="B7" s="1"/>
       <c r="C7" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D7" s="24"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
+      <c r="A8" s="23"/>
       <c r="B8" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="17"/>
+      <c r="E8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="18"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="1"/>
       <c r="C9" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="23"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="23"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
+      <c r="A11" s="23"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18"/>
+      <c r="A12" s="23"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19"/>
+      <c r="A13" s="24"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="16" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="14" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="1"/>
       <c r="C16" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="1"/>
       <c r="C17" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="1"/>
       <c r="C18" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="1"/>
       <c r="C19" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D20" s="16"/>
-      <c r="E20" s="14" t="s">
+      <c r="D20" s="17"/>
+      <c r="E20" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="1"/>
       <c r="C21" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="23"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D4:D7"/>
-    <mergeCell ref="D9:D13"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="D21:D25"/>
     <mergeCell ref="A2:A13"/>
     <mergeCell ref="A14:A25"/>
     <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C2:F2"/>
     <mergeCell ref="E3:E7"/>
     <mergeCell ref="F3:F7"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="E15:E19"/>
-    <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E20:E25"/>
     <mergeCell ref="F15:F19"/>
@@ -3918,6 +3917,10 @@
     <mergeCell ref="E8:E13"/>
     <mergeCell ref="F8:F13"/>
     <mergeCell ref="C14:F14"/>
+    <mergeCell ref="D4:D7"/>
+    <mergeCell ref="D9:D13"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="D21:D25"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F8 F15 F20" xr:uid="{015FF85D-4909-4B5A-8860-6B16B5CD0154}">
@@ -3965,184 +3968,184 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="1"/>
       <c r="C6" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="1"/>
       <c r="C7" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="1"/>
       <c r="C8" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="23"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="1"/>
       <c r="C9" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="17"/>
+      <c r="E10" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="23"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="1"/>
       <c r="C15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="23"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4203,410 +4206,410 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>27</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
+      <c r="A3" s="16"/>
       <c r="B3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="14" t="s">
+      <c r="D3" s="17"/>
+      <c r="E3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="14"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="1"/>
       <c r="C5" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="14"/>
+      <c r="A6" s="16"/>
       <c r="B6" s="1"/>
       <c r="C6" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="14"/>
+      <c r="A7" s="16"/>
       <c r="B7" s="1"/>
       <c r="C7" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="14"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="14"/>
+      <c r="A8" s="16"/>
       <c r="B8" s="1"/>
       <c r="C8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
+      <c r="A9" s="16"/>
       <c r="B9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="14" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="14"/>
+      <c r="A10" s="16"/>
       <c r="B10" s="1"/>
       <c r="C10" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="14"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="1"/>
       <c r="C11" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="14"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="1"/>
       <c r="C12" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D12" s="23"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="14"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="1"/>
       <c r="C13" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="1"/>
       <c r="C14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14"/>
+      <c r="A15" s="16"/>
       <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="14" t="s">
+      <c r="D15" s="17"/>
+      <c r="E15" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="14"/>
+      <c r="A16" s="16"/>
       <c r="B16" s="1"/>
       <c r="C16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
+      <c r="A17" s="16"/>
       <c r="B17" s="1"/>
       <c r="C17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D17" s="23"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="1"/>
       <c r="C18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="23"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
+      <c r="A19" s="16"/>
       <c r="B19" s="1"/>
       <c r="C19" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
+      <c r="A20" s="16"/>
       <c r="B20" s="1"/>
       <c r="C20" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="14"/>
+      <c r="A21" s="16"/>
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="14" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="14"/>
+      <c r="A22" s="16"/>
       <c r="B22" s="1"/>
       <c r="C22" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="14"/>
+      <c r="A23" s="16"/>
       <c r="B23" s="1"/>
       <c r="C23" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D23" s="23"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="14"/>
+      <c r="A24" s="16"/>
       <c r="B24" s="1"/>
       <c r="C24" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D24" s="23"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="14"/>
+      <c r="A25" s="16"/>
       <c r="B25" s="1"/>
       <c r="C25" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D25" s="24"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="22" t="s">
         <v>28</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="18"/>
+      <c r="A27" s="23"/>
       <c r="B27" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="16"/>
-      <c r="E27" s="14" t="s">
+      <c r="D27" s="17"/>
+      <c r="E27" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="18"/>
+      <c r="A28" s="23"/>
       <c r="B28" s="1"/>
       <c r="C28" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D28" s="22" t="s">
+      <c r="D28" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="18"/>
+      <c r="A29" s="23"/>
       <c r="B29" s="1"/>
       <c r="C29" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="23"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="18"/>
+      <c r="A30" s="23"/>
       <c r="B30" s="1"/>
       <c r="C30" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="24"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="16"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="18"/>
+      <c r="A31" s="23"/>
       <c r="B31" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="14" t="s">
+      <c r="D31" s="17"/>
+      <c r="E31" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F31" s="14" t="s">
+      <c r="F31" s="16" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="18"/>
+      <c r="A32" s="23"/>
       <c r="B32" s="1"/>
       <c r="C32" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="18"/>
+      <c r="A33" s="23"/>
       <c r="B33" s="1"/>
       <c r="C33" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="23"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="18"/>
+      <c r="A34" s="23"/>
       <c r="B34" s="1"/>
       <c r="C34" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D34" s="23"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="18"/>
+      <c r="A35" s="23"/>
       <c r="B35" s="1"/>
       <c r="C35" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="19"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="1"/>
       <c r="C36" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D36" s="24"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="28">
@@ -4626,18 +4629,18 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="A2:A25"/>
     <mergeCell ref="E3:E8"/>
-    <mergeCell ref="F3:F8"/>
-    <mergeCell ref="E9:E14"/>
-    <mergeCell ref="F9:F14"/>
-    <mergeCell ref="E15:E20"/>
-    <mergeCell ref="F15:F20"/>
+    <mergeCell ref="D16:D20"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="D4:D8"/>
     <mergeCell ref="D10:D14"/>
-    <mergeCell ref="D16:D20"/>
+    <mergeCell ref="F3:F8"/>
+    <mergeCell ref="E9:E14"/>
+    <mergeCell ref="F9:F14"/>
+    <mergeCell ref="E15:E20"/>
+    <mergeCell ref="F15:F20"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3 F9 F15 F27 F31 F21" xr:uid="{A794CFF3-DB8C-4190-9A56-4EFFA2D5433D}">
